--- a/Excel Dashbor.xlsx
+++ b/Excel Dashbor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f-moharami\Desktop\iPhone Sales Analytics Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f-moharami\Desktop\iPhone Sales Interactive Excel Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F76E6C-C1CC-42D3-84D2-85A60EC40AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5801B14A-7131-4675-A6BC-176D61BA1A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="iphone_sales_dataset" sheetId="2" r:id="rId1"/>
@@ -30,11 +30,11 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="297" r:id="rId4"/>
-    <pivotCache cacheId="300" r:id="rId5"/>
-    <pivotCache cacheId="303" r:id="rId6"/>
-    <pivotCache cacheId="306" r:id="rId7"/>
-    <pivotCache cacheId="309" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="4" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
@@ -56,7 +56,7 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A2CB5862-8E78-49c6-8D9D-AF26E26ADB89}">
       <x15:timelineCachePivotCaches>
-        <pivotCache cacheId="9" r:id="rId15"/>
+        <pivotCache cacheId="6" r:id="rId15"/>
       </x15:timelineCachePivotCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
@@ -694,1645 +694,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="586">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="40">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -10871,8 +9233,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>14567</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Country">
@@ -10895,7 +9257,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10949,8 +9311,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>53788</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="iPhone_Model">
@@ -10973,7 +9335,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11027,8 +9389,8 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>160244</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Storage">
@@ -11051,7 +9413,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11105,8 +9467,8 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>188259</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Color">
@@ -11129,7 +9491,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11183,8 +9545,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>25774</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Payment_Method">
@@ -11207,7 +9569,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11261,8 +9623,8 @@
       <xdr:row>54</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Sale_Date">
@@ -11280,12 +9642,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Sale_Date"/>
+              <tsle:timeslicer name="Sale_Date"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11495,8 +9857,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>68036</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="Country 1">
@@ -11519,7 +9881,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11573,8 +9935,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>40821</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="iPhone_Model 1">
@@ -11597,7 +9959,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11651,8 +10013,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>149680</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Storage 1">
@@ -11675,7 +10037,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11729,8 +10091,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>163287</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Color 1">
@@ -11753,7 +10115,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11807,8 +10169,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>122465</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Payment_Method 1">
@@ -11831,7 +10193,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11864,6 +10226,83 @@
                 <a:rPr lang="en-US" sz="1100"/>
                 <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
 If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="11" name="Sale_Date 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EF5E933-10C6-4B2E-88CF-A53317C0F41C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Sale_Date 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9344024" y="1"/>
+              <a:ext cx="6276975" cy="1276350"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -12418,271 +10857,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28863C3B-D40E-49B3-B95D-45E8C4D2CE82}" name="PivotTable4" cacheId="303" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A25:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
-      <items count="5">
-        <item x="0" e="0"/>
-        <item x="1" e="0"/>
-        <item x="2" e="0"/>
-        <item x="3" e="0"/>
-        <item x="4" e="0"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="551">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="550">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="549">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="548">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="547">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="546">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="19">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="12"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[SalesData]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B225A92D-A51E-491D-8420-5A0E520C2D4B}" name="PivotTable3" cacheId="300" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A14:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="557">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="556">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="555">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="554">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="553">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="552">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="19">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="3"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[SalesData]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4AA7FFB-05C8-4DBA-ABB0-C74BAEFD7CFC}" name="PivotTable2" cacheId="297" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4AA7FFB-05C8-4DBA-ABB0-C74BAEFD7CFC}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -12731,26 +10906,26 @@
     <dataField name="Sum of Revenue" fld="0" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="563">
+    <format dxfId="5">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="562">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="561">
+    <format dxfId="3">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="560">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="559">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="558">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -12816,8 +10991,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CBF5BF7-6803-435D-93EE-7D627EC8D51B}" name="PivotTable6" cacheId="309" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CBF5BF7-6803-435D-93EE-7D627EC8D51B}" name="PivotTable6" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F14:G15" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -12843,13 +11018,13 @@
     <dataField name="Sum of Revenue" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="566">
+    <format dxfId="8">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="565">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="564">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -12901,8 +11076,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E18C374-5B49-4D71-981C-411E0A3E521F}" name="PivotTable5" cacheId="306" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E18C374-5B49-4D71-981C-411E0A3E521F}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="F3:G8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -12943,26 +11118,26 @@
     <dataField name="Sum of Quantity" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="572">
+    <format dxfId="14">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="571">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="570">
+    <format dxfId="12">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="569">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="568">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="567">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -13106,6 +11281,270 @@
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
     <rowHierarchyUsage hierarchyUsage="10"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[SalesData]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28863C3B-D40E-49B3-B95D-45E8C4D2CE82}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A25:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="5">
+        <item x="0" e="0"/>
+        <item x="1" e="0"/>
+        <item x="2" e="0"/>
+        <item x="3" e="0"/>
+        <item x="4" e="0"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="20">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="19">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="12"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[SalesData]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B225A92D-A51E-491D-8420-5A0E520C2D4B}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A14:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="19">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="3"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -13328,20 +11767,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80F022DF-F8D5-491B-BE44-85B73249D456}" name="SalesData" displayName="SalesData" ref="A1:K101" tableType="queryTable" totalsRowShown="0" headerRowDxfId="585" dataDxfId="584">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80F022DF-F8D5-491B-BE44-85B73249D456}" name="SalesData" displayName="SalesData" ref="A1:K101" tableType="queryTable" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:K101" xr:uid="{80F022DF-F8D5-491B-BE44-85B73249D456}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{62692A1F-798C-4B03-A0A6-DE87A4260BF2}" uniqueName="1" name="Order_ID" queryTableFieldId="1" dataDxfId="583"/>
-    <tableColumn id="2" xr3:uid="{3E552723-6BAD-48DF-AB99-1F1AD4786B6B}" uniqueName="2" name="Customer_Name" queryTableFieldId="2" dataDxfId="582"/>
-    <tableColumn id="3" xr3:uid="{FB59C59C-3EB9-4B68-9334-4DA50ADDA4F0}" uniqueName="3" name="Country" queryTableFieldId="3" dataDxfId="581"/>
-    <tableColumn id="4" xr3:uid="{BCA949BE-BCD8-475A-931F-EB88D74A0879}" uniqueName="4" name="iPhone_Model" queryTableFieldId="4" dataDxfId="580"/>
-    <tableColumn id="5" xr3:uid="{B0571F9A-038E-4157-AEAE-FE0CB267A7DF}" uniqueName="5" name="Storage" queryTableFieldId="5" dataDxfId="579"/>
-    <tableColumn id="6" xr3:uid="{5AC76B4E-AED8-4792-BB6E-B87DFB0EC6CA}" uniqueName="6" name="Color" queryTableFieldId="6" dataDxfId="578"/>
-    <tableColumn id="7" xr3:uid="{51BC55BE-9053-42D1-9F79-EB6C62E64A00}" uniqueName="7" name="Quantity" queryTableFieldId="7" dataDxfId="577"/>
-    <tableColumn id="8" xr3:uid="{682F8F6A-E752-475B-ABFC-257028B6B4EF}" uniqueName="8" name="Price" queryTableFieldId="8" dataDxfId="576"/>
-    <tableColumn id="9" xr3:uid="{62B2970A-7158-4A22-A5C7-33520B86292B}" uniqueName="9" name="Sale_Date" queryTableFieldId="9" dataDxfId="575"/>
-    <tableColumn id="10" xr3:uid="{DA076650-9544-49E5-A515-F299DB04676F}" uniqueName="10" name="Payment_Method" queryTableFieldId="10" dataDxfId="574"/>
-    <tableColumn id="11" xr3:uid="{18189C8B-A858-49F6-A271-1EF1D914FF75}" uniqueName="11" name="Revenue" queryTableFieldId="11" dataDxfId="573">
+    <tableColumn id="1" xr3:uid="{62692A1F-798C-4B03-A0A6-DE87A4260BF2}" uniqueName="1" name="Order_ID" queryTableFieldId="1" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{3E552723-6BAD-48DF-AB99-1F1AD4786B6B}" uniqueName="2" name="Customer_Name" queryTableFieldId="2" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{FB59C59C-3EB9-4B68-9334-4DA50ADDA4F0}" uniqueName="3" name="Country" queryTableFieldId="3" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{BCA949BE-BCD8-475A-931F-EB88D74A0879}" uniqueName="4" name="iPhone_Model" queryTableFieldId="4" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{B0571F9A-038E-4157-AEAE-FE0CB267A7DF}" uniqueName="5" name="Storage" queryTableFieldId="5" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{5AC76B4E-AED8-4792-BB6E-B87DFB0EC6CA}" uniqueName="6" name="Color" queryTableFieldId="6" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{51BC55BE-9053-42D1-9F79-EB6C62E64A00}" uniqueName="7" name="Quantity" queryTableFieldId="7" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{682F8F6A-E752-475B-ABFC-257028B6B4EF}" uniqueName="8" name="Price" queryTableFieldId="8" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{62B2970A-7158-4A22-A5C7-33520B86292B}" uniqueName="9" name="Sale_Date" queryTableFieldId="9" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{DA076650-9544-49E5-A515-F299DB04676F}" uniqueName="10" name="Payment_Method" queryTableFieldId="10" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{18189C8B-A858-49F6-A271-1EF1D914FF75}" uniqueName="11" name="Revenue" queryTableFieldId="11" dataDxfId="27">
       <calculatedColumnFormula>SalesData[[#This Row],[Quantity]]*SalesData[[#This Row],[Price]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13625,6 +12064,12 @@
 </timelines>
 </file>
 
+<file path=xl/timelines/timeline2.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Sale_Date 1" xr10:uid="{3A7567EE-FBED-424B-8F53-7C402704B2B4}" cache="Timeline_Sale_Date" caption="Sale_Date" level="2" selectionLevel="2" scrollPosition="2025-01-01T00:00:00"/>
+</timelines>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853FA4A5-827A-42EB-923B-5F660EFCECFD}">
   <dimension ref="A1:K101"/>
@@ -17563,29 +16008,25 @@
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
     </row>
-    <row r="5" spans="17:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
     </row>
-    <row r="6" spans="17:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Q6" s="8" t="s">
+    <row r="6" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="17:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="17:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q8" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="R6" s="7">
+      <c r="R8" s="7">
         <f>GETPIVOTDATA("[Measures].[Sum of Revenue]",Pivot!$F$14)</f>
         <v>494453</v>
       </c>
-      <c r="S6" s="5"/>
-    </row>
-    <row r="7" spans="17:19" x14ac:dyDescent="0.25">
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-    </row>
-    <row r="8" spans="17:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="17:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17618,6 +16059,11 @@
         <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId4"/>
+      </x15:timelineRefs>
+    </ext>
   </extLst>
 </worksheet>
 </file>
